--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_404_Kenya.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_404_Kenya.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Rf85df655f14949f8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R98c8746459c1495c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R5943a31798b64043"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R5abb18c86cf94d22"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R20892953b5934cac"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="Re64ee08b3d584ea9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Ra5edda93d6754e57"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="Rd62c5f8ce0c949f1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R9746eca023bf481c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R54a6515c164046a5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="Rf26d2376170f4f56"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R136ed50581604db1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ404CommercialTable" displayName="EEZ404CommercialTable" ref="A1:O11" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O11"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ404CommercialTable" displayName="EEZ404CommercialTable" ref="A1:E11" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E11"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ404FunctionalTable" displayName="EEZ404FunctionalTable" ref="A1:O21" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O21"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ404FunctionalTable" displayName="EEZ404FunctionalTable" ref="A1:E21" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E21"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ404ValidationTable" displayName="EEZ404ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ404ValidationTable" displayName="EEZ404ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -8734,7 +8688,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfbe169aca0444ae2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re31e048d2c284b41"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8744,20 +8698,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -8765,606 +8709,212 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Anchovies</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>282.21993222730003</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.2106716538275415</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>162.43202322061808</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>282.21993222730003</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>163.0847501063954</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$121,A2,'Species'!$U$2:$U$121))</x:f>
-        <x:v>46025.767122333076</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.2106716538275415</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>162.43202322061808</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>45841.55458486606</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>184.21253746701404</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.0040184618330512</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.004018461833051124</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>1048.3587953452</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>2.986860868648432</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>97.01991027458813</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>1048.3587953452</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>112.77598676842321</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$121,A3,'Species'!$U$2:$U$121))</x:f>
-        <x:v>118229.69763241036</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>2.986860868648432</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>97.01991027458813</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>101711.6762599666</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>16518.021372443764</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.1624004438804556</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.1624004438804555</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>90.5291171133</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.635772303269035</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>432.2871273180068</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>90.5291171133</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>538.6268528487958</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$121,A4,'Species'!$U$2:$U$121))</x:f>
-        <x:v>48761.41344191684</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.635772303269035</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>432.2871273180068</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>39134.57197554387</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>9626.84146637297</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.245993273476685</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.24599327347668487</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>1069.0966517503002</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.4164322976011423</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>260.87490120362406</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>1069.0966517503002</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>550.3035933104736</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$121,A5,'Species'!$U$2:$U$121))</x:f>
-        <x:v>588327.7290543863</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.4164322976011423</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>260.87490120362406</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>278900.48340248485</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>309427.2456519014</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>2.1094539596238815</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>1.1094539596238813</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>223.3383008566</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>2.1</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>12.589254117941675</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>223.3383008566</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>12.589254117941675</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$121,A6,'Species'!$U$2:$U$121))</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>2811.662623753048</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>2.1</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>12.589254117941675</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
-        <x:v>2811.662623753048</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>9702.1606912912</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.330928950508252</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>214.25400582484855</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>9702.1606912912</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>261.72047538071917</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$121,A7,'Species'!$U$2:$U$121))</x:f>
-        <x:v>2539254.1083448594</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.330928950508252</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>214.25400582484855</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>2078726.7932655213</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>460527.31507933815</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.2215429735987022</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.22154297359870215</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>13985.522787458103</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.3775776296719733</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>238.54901611607673</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>13985.522787458103</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>829.5016139234444</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$121,A8,'Species'!$U$2:$U$121))</x:f>
-        <x:v>11601013.723759606</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.3775776296719733</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>238.54901611607673</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>3336232.7008171016</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>8264781.022942505</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>3.477279543755541</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>2.477279543755541</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Scorpionfishes</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>32.789769679</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.881152665620405</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>760.5935980593621</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>32.789769679</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>769.4358651087296</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$121,A9,'Species'!$U$2:$U$121))</x:f>
-        <x:v>25229.624799677356</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.881152665620405</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>760.5935980593621</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>24939.688899688386</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>289.93589998897005</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.0116254818235761</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.011625481823576103</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>2498.1564505325</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.9563345657928624</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>904.3458829507018</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>2498.1564505325</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>1015.4715866124831</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$H$2:$H$121,A10,'Species'!$U$2:$U$121))</x:f>
-        <x:v>2536806.894428447</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.9563345657928624</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>904.3458829507018</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>2259197.501005805</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>277609.3934226418</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.1228796478833962</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.12287964788339613</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>1402.1633563349</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>4.471436308676833</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>2960.985691108555</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>1402.1633563349</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>2990.2943609076715</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$H$2:$H$121,A11,'Species'!$U$2:$U$121))</x:f>
-        <x:v>4192881.1775196255</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>4.471436308676833</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>2960.985691108555</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>4151785.634704385</x:v>
       </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>41095.542815240566</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.00989828146996</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.009898281469960009</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G11">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O11">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5071c42a793a40df"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R85b800b66ba94af7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9374,20 +8924,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -9395,1146 +8935,402 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cephalopods</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>1942.8722358303003</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.70083000117579</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>502.1459926476437</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>1942.8722358303003</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>583.3632694098642</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$121,A2,'Species'!$U$2:$U$121))</x:f>
-        <x:v>1133400.2995396166</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.70083000117579</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>502.1459926476437</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>975605.5074485531</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>157794.79209106346</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.1617403662508379</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.16174036625083782</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Jellyfish</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>6.2022544277</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>2.5</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>31.622776601683793</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>6.2022544277</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>31.622776601683793</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$121,A3,'Species'!$U$2:$U$121))</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>196.13250619396126</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>2.5</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>31.622776601683793</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
-        <x:v>196.13250619396126</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>226.00430391180004</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>4.372812929229105</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>2359.4616847069515</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>226.00430391180004</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>2393.0821498112396</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$121,A4,'Species'!$U$2:$U$121))</x:f>
-        <x:v>540846.8654718432</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>4.372812929229105</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>2359.4616847069515</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>533248.4956587576</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>7598.369813085534</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.014249210030492</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.014249210030491991</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>2.9738487581</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>4.18</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>1513.5612484362073</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>2.9738487581</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>1513.5612484362073</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$121,A5,'Species'!$U$2:$U$121))</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>4501.1022389703</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>4.18</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>1513.5612484362073</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
-        <x:v>4501.1022389703</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>2497.5863529462</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>4.456823782896467</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>2863.0160514733193</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>2497.5863529462</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>2908.247894522194</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$121,A6,'Species'!$U$2:$U$121))</x:f>
-        <x:v>7263600.252343152</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>4.456823782896467</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>2863.0160514733193</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>7150629.818425677</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>112970.43391747493</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0157986690384075</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.015798669038407466</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Large rays (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>1012.9104541319999</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.72</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>524.8074602497728</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>1012.9104541319999</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>524.8074602497728</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$121,A7,'Species'!$U$2:$U$121))</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>531582.9628934589</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.72</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>524.8074602497728</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
-        <x:v>531582.9628934589</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Large reef assoc. fish (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>34.4394762697</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.637554763951649</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>434.0649952075673</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>34.4394762697</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>1309.3918584504224</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$121,A8,'Species'!$U$2:$U$121))</x:f>
-        <x:v>45094.769836841704</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.637554763951649</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>434.0649952075673</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>14948.971101958457</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>30145.798734883247</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>3.0165801732624837</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>2.0165801732624837</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>1485.2459964005002</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>4.1175103931941734</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>1310.7214091452531</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>1485.2459964005002</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>1350.0954969039853</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$121,A9,'Species'!$U$2:$U$121))</x:f>
-        <x:v>2005223.931534988</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>4.1175103931941734</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>1310.7214091452531</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>1946743.7253294091</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>58480.20620557899</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.0300400126861504</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.030040012686150322</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>666.7290165505</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.1691066604284694</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>147.60690035063894</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>666.7290165505</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>149.21313841377273</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$121,A10,'Species'!$U$2:$U$121))</x:f>
-        <x:v>99484.72903102831</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.1691066604284694</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>147.60690035063894</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>98413.80350684914</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>1070.9255241791689</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.010881862970621</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.010881862970621162</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>59.148048444699995</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.5369287655304325</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>344.2934539392426</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>59.148048444699995</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>355.92917939960347</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$121,A11,'Species'!$U$2:$U$121))</x:f>
-        <x:v>21052.516346010063</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.5369287655304325</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>344.2934539392426</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>20364.28589279141</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>688.2304532186536</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.033795953211513</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.03379595321151304</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>7109.3996051673</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>3.2983481881288337</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>198.76878732637888</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>7109.3996051673</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>207.17949974970966</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$121,A12,'Species'!$U$2:$U$121))</x:f>
-        <x:v>1472921.8537193446</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>3.2983481881288337</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>198.76878732637888</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>1413126.738137741</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>59795.11558160349</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.0423140500903714</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.042314050090371376</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>3442.2293539828</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>3.7047892332821335</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>506.74472116922817</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>3442.2293539828</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>908.7553933969239</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$121,A13,'Species'!$U$2:$U$121))</x:f>
-        <x:v>3128144.4907410787</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>3.7047892332821335</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>506.74472116922817</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>1744331.5541845465</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>1383812.9365565323</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.793319901389646</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0.7933199013896459</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>9045.674081684001</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>3.1270380103758044</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>133.97939439072314</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>9045.674081684001</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>562.154639266451</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$121,A14,'Species'!$U$2:$U$121))</x:f>
-        <x:v>5085067.650310955</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>3.1270380103758044</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>133.97939439072314</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>1211933.9353198833</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>3873133.7149910717</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>4.195829081202169</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>3.1958290812021692</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>223.3383008566</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>2.1</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>12.589254117941675</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>223.3383008566</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>12.589254117941675</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$121,A15,'Species'!$U$2:$U$121))</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>2811.662623753048</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>2.1</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>12.589254117941675</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
-        <x:v>2811.662623753048</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>381.6297787947</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>2.668467063249568</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>46.60870787709624</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>381.6297787947</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>49.11820209781382</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$121,A16,'Species'!$U$2:$U$121))</x:f>
-        <x:v>18744.968601382057</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>2.668467063249568</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>46.60870787709624</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>17787.27087704303</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>957.6977243390284</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>1.053841746210492</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>0.05384174621049212</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="24" t="str">
         <x:v>Small benthopelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B17" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="B17" s="31" t="n">
         <x:v>420.61130967919996</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="n">
+        <x:v>3.075543544552552</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="n">
+        <x:f>IF(C17="","",(1/'Metadata'!$B$5)^(C17-1))</x:f>
+        <x:v>118.99906376347175</x:v>
+      </x:c>
       <x:c r="E17" s="31" t="n">
-        <x:v>420.61130967919996</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="32" t="n">
-        <x:f>IF(E17=0,"",I17/E17)</x:f>
-        <x:v>124.61570228718402</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="n">
-        <x:f>IF(C17=0,"",SUMIF('Species'!$G$2:$G$121,A17,'Species'!$U$2:$U$121))</x:f>
-        <x:v>52414.773745605744</x:v>
-      </x:c>
-      <x:c r="J17" s="32" t="n">
-        <x:v>3.075543544552552</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>IF(J17="","",(1/'Metadata'!$B$5)^(J17-1))</x:f>
-        <x:v>118.99906376347175</x:v>
-      </x:c>
-      <x:c r="L17" s="31" t="n">
-        <x:f>IF(E17=0,"",E17*K17)</x:f>
+        <x:f>IF(B17=0,"",B17*D17)</x:f>
         <x:v>50052.35206015248</x:v>
-      </x:c>
-      <x:c r="M17" s="31" t="n">
-        <x:f>IF(E17=0,"",I17-L17)</x:f>
-        <x:v>2362.421685453264</x:v>
-      </x:c>
-      <x:c r="N17" s="32" t="n">
-        <x:f>IF(L17=0,"",I17/L17)</x:f>
-        <x:v>1.047199014396249</x:v>
-      </x:c>
-      <x:c r="O17" s="34" t="n">
-        <x:f>IF(L17=0,"",M17/L17)</x:f>
-        <x:v>0.04719901439624908</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="18" customHeight="1">
       <x:c r="A18" s="24" t="str">
         <x:v>Small demersals (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B18" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C18" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D18" s="31" t="n">
+      <x:c r="B18" s="31" t="n">
         <x:v>92.28234510380001</x:v>
       </x:c>
+      <x:c r="C18" s="32" t="n">
+        <x:v>3.5123997549118506</x:v>
+      </x:c>
+      <x:c r="D18" s="32" t="n">
+        <x:f>IF(C18="","",(1/'Metadata'!$B$5)^(C18-1))</x:f>
+        <x:v>325.3866681525412</x:v>
+      </x:c>
       <x:c r="E18" s="31" t="n">
-        <x:v>92.28234510380001</x:v>
-      </x:c>
-      <x:c r="F18" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G18" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H18" s="32" t="n">
-        <x:f>IF(E18=0,"",I18/E18)</x:f>
-        <x:v>446.4530927693907</x:v>
-      </x:c>
-      <x:c r="I18" s="31" t="n">
-        <x:f>IF(C18=0,"",SUMIF('Species'!$G$2:$G$121,A18,'Species'!$U$2:$U$121))</x:f>
-        <x:v>41199.738379603754</x:v>
-      </x:c>
-      <x:c r="J18" s="32" t="n">
-        <x:v>3.5123997549118506</x:v>
-      </x:c>
-      <x:c r="K18" s="32" t="n">
-        <x:f>IF(J18="","",(1/'Metadata'!$B$5)^(J18-1))</x:f>
-        <x:v>325.3866681525412</x:v>
-      </x:c>
-      <x:c r="L18" s="31" t="n">
-        <x:f>IF(E18=0,"",E18*K18)</x:f>
+        <x:f>IF(B18=0,"",B18*D18)</x:f>
         <x:v>30027.44480262846</x:v>
-      </x:c>
-      <x:c r="M18" s="31" t="n">
-        <x:f>IF(E18=0,"",I18-L18)</x:f>
-        <x:v>11172.293576975295</x:v>
-      </x:c>
-      <x:c r="N18" s="32" t="n">
-        <x:f>IF(L18=0,"",I18/L18)</x:f>
-        <x:v>1.372069406851339</x:v>
-      </x:c>
-      <x:c r="O18" s="34" t="n">
-        <x:f>IF(L18=0,"",M18/L18)</x:f>
-        <x:v>0.37206940685133905</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="18" customHeight="1">
       <x:c r="A19" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B19" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C19" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D19" s="31" t="n">
+      <x:c r="B19" s="31" t="n">
         <x:v>1156.9840929606</x:v>
       </x:c>
+      <x:c r="C19" s="32" t="n">
+        <x:v>3.177889994929107</x:v>
+      </x:c>
+      <x:c r="D19" s="32" t="n">
+        <x:f>IF(C19="","",(1/'Metadata'!$B$5)^(C19-1))</x:f>
+        <x:v>150.62254969155092</x:v>
+      </x:c>
       <x:c r="E19" s="31" t="n">
-        <x:v>1156.9840929606</x:v>
-      </x:c>
-      <x:c r="F19" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G19" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H19" s="32" t="n">
-        <x:f>IF(E19=0,"",I19/E19)</x:f>
-        <x:v>154.98591289456306</x:v>
-      </x:c>
-      <x:c r="I19" s="31" t="n">
-        <x:f>IF(C19=0,"",SUMIF('Species'!$G$2:$G$121,A19,'Species'!$U$2:$U$121))</x:f>
-        <x:v>179316.2358519866</x:v>
-      </x:c>
-      <x:c r="J19" s="32" t="n">
-        <x:v>3.177889994929107</x:v>
-      </x:c>
-      <x:c r="K19" s="32" t="n">
-        <x:f>IF(J19="","",(1/'Metadata'!$B$5)^(J19-1))</x:f>
-        <x:v>150.62254969155092</x:v>
-      </x:c>
-      <x:c r="L19" s="31" t="n">
-        <x:f>IF(E19=0,"",E19*K19)</x:f>
+        <x:f>IF(B19=0,"",B19*D19)</x:f>
         <x:v>174267.89403429194</x:v>
-      </x:c>
-      <x:c r="M19" s="31" t="n">
-        <x:f>IF(E19=0,"",I19-L19)</x:f>
-        <x:v>5048.341817694658</x:v>
-      </x:c>
-      <x:c r="N19" s="32" t="n">
-        <x:f>IF(L19=0,"",I19/L19)</x:f>
-        <x:v>1.0289688576640585</x:v>
-      </x:c>
-      <x:c r="O19" s="34" t="n">
-        <x:f>IF(L19=0,"",M19/L19)</x:f>
-        <x:v>0.028968857664058646</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="18" customHeight="1">
       <x:c r="A20" s="24" t="str">
         <x:v>Small reef assoc. fish (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B20" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C20" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D20" s="31" t="n">
+      <x:c r="B20" s="31" t="n">
         <x:v>437.54587957459995</x:v>
       </x:c>
+      <x:c r="C20" s="32" t="n">
+        <x:v>2.4112642852131887</x:v>
+      </x:c>
+      <x:c r="D20" s="32" t="n">
+        <x:f>IF(C20="","",(1/'Metadata'!$B$5)^(C20-1))</x:f>
+        <x:v>25.7788942652661</x:v>
+      </x:c>
       <x:c r="E20" s="31" t="n">
-        <x:v>437.54587957459995</x:v>
-      </x:c>
-      <x:c r="F20" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G20" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H20" s="32" t="n">
-        <x:f>IF(E20=0,"",I20/E20)</x:f>
-        <x:v>57.08075595080992</x:v>
-      </x:c>
-      <x:c r="I20" s="31" t="n">
-        <x:f>IF(C20=0,"",SUMIF('Species'!$G$2:$G$121,A20,'Species'!$U$2:$U$121))</x:f>
-        <x:v>24975.44956928021</x:v>
-      </x:c>
-      <x:c r="J20" s="32" t="n">
-        <x:v>2.4112642852131887</x:v>
-      </x:c>
-      <x:c r="K20" s="32" t="n">
-        <x:f>IF(J20="","",(1/'Metadata'!$B$5)^(J20-1))</x:f>
-        <x:v>25.7788942652661</x:v>
-      </x:c>
-      <x:c r="L20" s="31" t="n">
-        <x:f>IF(E20=0,"",E20*K20)</x:f>
+        <x:f>IF(B20=0,"",B20*D20)</x:f>
         <x:v>11279.448965756466</x:v>
-      </x:c>
-      <x:c r="M20" s="31" t="n">
-        <x:f>IF(E20=0,"",I20-L20)</x:f>
-        <x:v>13696.000603523742</x:v>
-      </x:c>
-      <x:c r="N20" s="32" t="n">
-        <x:f>IF(L20=0,"",I20/L20)</x:f>
-        <x:v>2.214243767147113</x:v>
-      </x:c>
-      <x:c r="O20" s="34" t="n">
-        <x:f>IF(L20=0,"",M20/L20)</x:f>
-        <x:v>1.2142437671471134</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="18" customHeight="1">
       <x:c r="A21" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B21" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C21" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D21" s="31" t="n">
+      <x:c r="B21" s="31" t="n">
         <x:v>90.5291171133</x:v>
       </x:c>
+      <x:c r="C21" s="32" t="n">
+        <x:v>3.635772303269035</x:v>
+      </x:c>
+      <x:c r="D21" s="32" t="n">
+        <x:f>IF(C21="","",(1/'Metadata'!$B$5)^(C21-1))</x:f>
+        <x:v>432.2871273180068</x:v>
+      </x:c>
       <x:c r="E21" s="31" t="n">
-        <x:v>90.5291171133</x:v>
-      </x:c>
-      <x:c r="F21" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G21" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H21" s="32" t="n">
-        <x:f>IF(E21=0,"",I21/E21)</x:f>
-        <x:v>538.6268528487958</x:v>
-      </x:c>
-      <x:c r="I21" s="31" t="n">
-        <x:f>IF(C21=0,"",SUMIF('Species'!$G$2:$G$121,A21,'Species'!$U$2:$U$121))</x:f>
-        <x:v>48761.41344191684</x:v>
-      </x:c>
-      <x:c r="J21" s="32" t="n">
-        <x:v>3.635772303269035</x:v>
-      </x:c>
-      <x:c r="K21" s="32" t="n">
-        <x:f>IF(J21="","",(1/'Metadata'!$B$5)^(J21-1))</x:f>
-        <x:v>432.2871273180068</x:v>
-      </x:c>
-      <x:c r="L21" s="31" t="n">
-        <x:f>IF(E21=0,"",E21*K21)</x:f>
+        <x:f>IF(B21=0,"",B21*D21)</x:f>
         <x:v>39134.57197554387</x:v>
       </x:c>
-      <x:c r="M21" s="31" t="n">
-        <x:f>IF(E21=0,"",I21-L21)</x:f>
-        <x:v>9626.84146637297</x:v>
-      </x:c>
-      <x:c r="N21" s="32" t="n">
-        <x:f>IF(L21=0,"",I21/L21)</x:f>
-        <x:v>1.245993273476685</x:v>
-      </x:c>
-      <x:c r="O21" s="34" t="n">
-        <x:f>IF(L21=0,"",M21/L21)</x:f>
-        <x:v>0.24599327347668487</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G21">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O21">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R542ecdcc7fa6461a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra55f364aa5864522"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10709,7 +9505,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -10808,7 +9604,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>21699341.798727013</x:v>
+        <x:v>12319282.267539116</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -10822,7 +9618,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>21699341.798727013</x:v>
+        <x:v>15970987.67798396</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -10836,7 +9632,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>3.725290298461914e-9</x:v>
+        <x:v>-9380059.531187894</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -10850,7 +9646,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>3.725290298461914e-9</x:v>
+        <x:v>-5728354.120743049</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -10861,9 +9657,9 @@
         <x:v>EEZ_404</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -10875,47 +9671,19 @@
         <x:v>EEZ_404</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_404</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_404</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8b581569878e4d02"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4f330b12743a446b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10962,7 +9730,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
